--- a/vibration_python/弹簧参数组合.xlsx
+++ b/vibration_python/弹簧参数组合.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S120"/>
+  <dimension ref="A1:O120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,54 +476,34 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>L0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>delta_target</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>delta1_target</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>delta2_target</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>delta3_target</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>h_target</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>h1_target</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>h2_target</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>d_target</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>delta_target</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>delta1_target</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>delta2_target</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -554,34 +534,22 @@
         <v>14.010272755249</v>
       </c>
       <c r="J2" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K2" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L2" t="n">
-        <v>9.833827318713158</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M2" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N2" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O2" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P2" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R2" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713157</v>
       </c>
     </row>
     <row r="3">
@@ -613,34 +581,22 @@
         <v>14.00525474924783</v>
       </c>
       <c r="J3" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K3" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L3" t="n">
-        <v>9.833827318713148</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M3" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N3" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O3" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P3" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R3" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713151</v>
       </c>
     </row>
     <row r="4">
@@ -672,34 +628,22 @@
         <v>14.00024033651986</v>
       </c>
       <c r="J4" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K4" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L4" t="n">
-        <v>9.833827318713146</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M4" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N4" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O4" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P4" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R4" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713155</v>
       </c>
     </row>
     <row r="5">
@@ -731,34 +675,22 @@
         <v>13.99522951320685</v>
       </c>
       <c r="J5" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K5" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L5" t="n">
-        <v>9.833827318713144</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M5" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N5" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O5" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P5" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R5" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713148</v>
       </c>
     </row>
     <row r="6">
@@ -790,34 +722,22 @@
         <v>13.99022227545616</v>
       </c>
       <c r="J6" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K6" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L6" t="n">
-        <v>9.833827318713153</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M6" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N6" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O6" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P6" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R6" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713151</v>
       </c>
     </row>
     <row r="7">
@@ -849,34 +769,22 @@
         <v>13.98521861942059</v>
       </c>
       <c r="J7" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K7" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L7" t="n">
-        <v>9.833827318713151</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M7" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N7" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O7" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P7" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R7" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713144</v>
       </c>
     </row>
     <row r="8">
@@ -908,34 +816,22 @@
         <v>13.98021854125848</v>
       </c>
       <c r="J8" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K8" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L8" t="n">
-        <v>9.83382731871315</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M8" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N8" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O8" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P8" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R8" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713148</v>
       </c>
     </row>
     <row r="9">
@@ -967,34 +863,22 @@
         <v>13.97522203713365</v>
       </c>
       <c r="J9" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K9" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L9" t="n">
-        <v>9.833827318713157</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M9" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N9" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O9" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P9" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R9" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713142</v>
       </c>
     </row>
     <row r="10">
@@ -1026,34 +910,22 @@
         <v>13.97022910321542</v>
       </c>
       <c r="J10" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K10" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L10" t="n">
-        <v>9.833827318713155</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M10" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N10" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O10" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P10" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R10" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713153</v>
       </c>
     </row>
     <row r="11">
@@ -1085,34 +957,22 @@
         <v>13.96523973567856</v>
       </c>
       <c r="J11" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K11" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L11" t="n">
-        <v>9.833827318713153</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M11" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N11" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O11" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P11" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R11" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713148</v>
       </c>
     </row>
     <row r="12">
@@ -1144,34 +1004,22 @@
         <v>13.9602539307033</v>
       </c>
       <c r="J12" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K12" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L12" t="n">
+        <v>39.73509933774834</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.550991765900781</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-36.14204360727691</v>
+      </c>
+      <c r="O12" t="n">
         <v>9.833827318713151</v>
-      </c>
-      <c r="M12" t="n">
-        <v>97.70163735096665</v>
-      </c>
-      <c r="N12" t="n">
-        <v>52.11057932438398</v>
-      </c>
-      <c r="O12" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P12" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R12" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-36.14204360727691</v>
       </c>
     </row>
     <row r="13">
@@ -1203,34 +1051,22 @@
         <v>13.95527168447536</v>
       </c>
       <c r="J13" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K13" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L13" t="n">
-        <v>9.833827318713139</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M13" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N13" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O13" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P13" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R13" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713135</v>
       </c>
     </row>
     <row r="14">
@@ -1262,34 +1098,22 @@
         <v>13.95029299318586</v>
       </c>
       <c r="J14" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K14" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L14" t="n">
-        <v>9.833827318713148</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M14" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N14" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O14" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P14" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R14" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713157</v>
       </c>
     </row>
     <row r="15">
@@ -1321,34 +1145,22 @@
         <v>13.94531785303137</v>
       </c>
       <c r="J15" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K15" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L15" t="n">
-        <v>9.833827318713146</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M15" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N15" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O15" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P15" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R15" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.83382731871316</v>
       </c>
     </row>
     <row r="16">
@@ -1380,34 +1192,22 @@
         <v>13.94034626021389</v>
       </c>
       <c r="J16" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K16" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L16" t="n">
-        <v>9.833827318713164</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M16" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N16" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O16" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P16" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R16" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713153</v>
       </c>
     </row>
     <row r="17">
@@ -1439,34 +1239,22 @@
         <v>13.93537821094083</v>
       </c>
       <c r="J17" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K17" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L17" t="n">
-        <v>9.833827318713142</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M17" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N17" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O17" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P17" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713157</v>
       </c>
     </row>
     <row r="18">
@@ -1498,34 +1286,22 @@
         <v>13.93041370142499</v>
       </c>
       <c r="J18" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K18" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L18" t="n">
+        <v>39.73509933774834</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.550991765900781</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-36.14204360727691</v>
+      </c>
+      <c r="O18" t="n">
         <v>9.833827318713151</v>
-      </c>
-      <c r="M18" t="n">
-        <v>97.70163735096665</v>
-      </c>
-      <c r="N18" t="n">
-        <v>52.11057932438398</v>
-      </c>
-      <c r="O18" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P18" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R18" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-36.14204360727691</v>
       </c>
     </row>
     <row r="19">
@@ -1557,34 +1333,22 @@
         <v>15.90272840137106</v>
       </c>
       <c r="J19" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K19" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L19" t="n">
-        <v>9.83382731871315</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M19" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N19" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O19" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P19" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R19" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713155</v>
       </c>
     </row>
     <row r="20">
@@ -1616,34 +1380,22 @@
         <v>15.89755341653495</v>
       </c>
       <c r="J20" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K20" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L20" t="n">
+        <v>39.73509933774834</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4.550991765900781</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-36.14204360727691</v>
+      </c>
+      <c r="O20" t="n">
         <v>9.833827318713157</v>
-      </c>
-      <c r="M20" t="n">
-        <v>97.70163735096665</v>
-      </c>
-      <c r="N20" t="n">
-        <v>52.11057932438398</v>
-      </c>
-      <c r="O20" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P20" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R20" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S20" t="n">
-        <v>-36.14204360727691</v>
       </c>
     </row>
     <row r="21">
@@ -1675,34 +1427,22 @@
         <v>15.89238179863757</v>
       </c>
       <c r="J21" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K21" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L21" t="n">
-        <v>9.833827318713148</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M21" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N21" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O21" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P21" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R21" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713151</v>
       </c>
     </row>
     <row r="22">
@@ -1734,34 +1474,22 @@
         <v>15.88721354439411</v>
       </c>
       <c r="J22" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K22" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L22" t="n">
+        <v>39.73509933774834</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4.550991765900781</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-36.14204360727691</v>
+      </c>
+      <c r="O22" t="n">
         <v>9.833827318713146</v>
-      </c>
-      <c r="M22" t="n">
-        <v>97.70163735096665</v>
-      </c>
-      <c r="N22" t="n">
-        <v>52.11057932438398</v>
-      </c>
-      <c r="O22" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P22" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R22" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S22" t="n">
-        <v>-36.14204360727691</v>
       </c>
     </row>
     <row r="23">
@@ -1793,34 +1521,22 @@
         <v>15.88204865052402</v>
       </c>
       <c r="J23" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K23" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L23" t="n">
-        <v>9.833827318713153</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M23" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N23" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O23" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P23" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R23" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S23" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713157</v>
       </c>
     </row>
     <row r="24">
@@ -1852,34 +1568,22 @@
         <v>15.87688711375102</v>
       </c>
       <c r="J24" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K24" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L24" t="n">
-        <v>9.833827318713141</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M24" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N24" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O24" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P24" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R24" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S24" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.83382731871315</v>
       </c>
     </row>
     <row r="25">
@@ -1911,34 +1615,22 @@
         <v>15.87172893080309</v>
       </c>
       <c r="J25" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K25" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L25" t="n">
-        <v>9.833827318713148</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M25" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N25" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O25" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P25" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R25" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S25" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713153</v>
       </c>
     </row>
     <row r="26">
@@ -1970,34 +1662,22 @@
         <v>15.86657409841244</v>
       </c>
       <c r="J26" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K26" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L26" t="n">
+        <v>39.73509933774834</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4.550991765900781</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-36.14204360727691</v>
+      </c>
+      <c r="O26" t="n">
         <v>9.833827318713148</v>
-      </c>
-      <c r="M26" t="n">
-        <v>97.70163735096665</v>
-      </c>
-      <c r="N26" t="n">
-        <v>52.11057932438398</v>
-      </c>
-      <c r="O26" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P26" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R26" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S26" t="n">
-        <v>-36.14204360727691</v>
       </c>
     </row>
     <row r="27">
@@ -2029,34 +1709,22 @@
         <v>15.86142261331555</v>
       </c>
       <c r="J27" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K27" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L27" t="n">
-        <v>9.833827318713164</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M27" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N27" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O27" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P27" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R27" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S27" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713151</v>
       </c>
     </row>
     <row r="28">
@@ -2088,34 +1756,22 @@
         <v>15.85627447225313</v>
       </c>
       <c r="J28" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K28" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L28" t="n">
-        <v>9.833827318713153</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M28" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N28" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O28" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P28" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R28" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S28" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713146</v>
       </c>
     </row>
     <row r="29">
@@ -2147,34 +1803,22 @@
         <v>15.85112967197012</v>
       </c>
       <c r="J29" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K29" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L29" t="n">
-        <v>9.833827318713142</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M29" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N29" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O29" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P29" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R29" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S29" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713139</v>
       </c>
     </row>
     <row r="30">
@@ -2206,34 +1850,22 @@
         <v>15.84598820921566</v>
       </c>
       <c r="J30" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K30" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L30" t="n">
-        <v>9.83382731871315</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M30" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N30" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O30" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P30" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R30" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S30" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713142</v>
       </c>
     </row>
     <row r="31">
@@ -2265,34 +1897,22 @@
         <v>15.84085008074316</v>
       </c>
       <c r="J31" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K31" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L31" t="n">
-        <v>9.83382731871315</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M31" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N31" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O31" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P31" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R31" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S31" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713153</v>
       </c>
     </row>
     <row r="32">
@@ -2324,34 +1944,22 @@
         <v>15.83571528331018</v>
       </c>
       <c r="J32" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K32" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L32" t="n">
-        <v>9.833827318713148</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M32" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N32" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O32" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P32" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R32" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S32" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713157</v>
       </c>
     </row>
     <row r="33">
@@ -2383,34 +1991,22 @@
         <v>15.83058381367852</v>
       </c>
       <c r="J33" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K33" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L33" t="n">
-        <v>9.833827318713146</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M33" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N33" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O33" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P33" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R33" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S33" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713142</v>
       </c>
     </row>
     <row r="34">
@@ -2442,34 +2038,22 @@
         <v>15.82545566861415</v>
       </c>
       <c r="J34" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K34" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L34" t="n">
-        <v>9.83382731871316</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M34" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N34" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O34" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P34" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R34" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S34" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713153</v>
       </c>
     </row>
     <row r="35">
@@ -2501,34 +2085,22 @@
         <v>15.82033084488727</v>
       </c>
       <c r="J35" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K35" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L35" t="n">
-        <v>9.833827318713158</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M35" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N35" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O35" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P35" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R35" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S35" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713148</v>
       </c>
     </row>
     <row r="36">
@@ -2560,34 +2132,22 @@
         <v>15.81520933927222</v>
       </c>
       <c r="J36" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K36" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L36" t="n">
-        <v>9.833827318713141</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M36" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N36" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O36" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P36" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R36" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S36" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713158</v>
       </c>
     </row>
     <row r="37">
@@ -2619,34 +2179,22 @@
         <v>15.81009114854754</v>
       </c>
       <c r="J37" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K37" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L37" t="n">
-        <v>9.833827318713157</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M37" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N37" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O37" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P37" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R37" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S37" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713153</v>
       </c>
     </row>
     <row r="38">
@@ -2678,34 +2226,22 @@
         <v>15.80497626949592</v>
       </c>
       <c r="J38" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K38" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L38" t="n">
-        <v>9.833827318713146</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M38" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N38" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O38" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P38" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R38" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S38" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713155</v>
       </c>
     </row>
     <row r="39">
@@ -2737,34 +2273,22 @@
         <v>18.26055568808559</v>
       </c>
       <c r="J39" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K39" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L39" t="n">
-        <v>9.833827318713146</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M39" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N39" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O39" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P39" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R39" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S39" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713148</v>
       </c>
     </row>
     <row r="40">
@@ -2796,34 +2320,22 @@
         <v>18.2552116565702</v>
       </c>
       <c r="J40" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K40" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L40" t="n">
-        <v>9.833827318713153</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M40" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N40" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O40" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P40" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R40" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S40" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713142</v>
       </c>
     </row>
     <row r="41">
@@ -2855,34 +2367,22 @@
         <v>18.24987075204809</v>
       </c>
       <c r="J41" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K41" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L41" t="n">
-        <v>9.83382731871316</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M41" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N41" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O41" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P41" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R41" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S41" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713153</v>
       </c>
     </row>
     <row r="42">
@@ -2914,34 +2414,22 @@
         <v>18.24453297177548</v>
       </c>
       <c r="J42" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K42" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L42" t="n">
-        <v>9.833827318713142</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M42" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N42" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O42" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P42" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R42" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S42" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713148</v>
       </c>
     </row>
     <row r="43">
@@ -2973,34 +2461,22 @@
         <v>18.2391983130118</v>
       </c>
       <c r="J43" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K43" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L43" t="n">
-        <v>9.83382731871315</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M43" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N43" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O43" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P43" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R43" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S43" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713142</v>
       </c>
     </row>
     <row r="44">
@@ -3032,34 +2508,22 @@
         <v>18.23386677301969</v>
       </c>
       <c r="J44" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K44" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L44" t="n">
-        <v>9.833827318713148</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M44" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N44" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O44" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P44" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R44" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S44" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713153</v>
       </c>
     </row>
     <row r="45">
@@ -3091,34 +2555,22 @@
         <v>18.22853834906499</v>
       </c>
       <c r="J45" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K45" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L45" t="n">
-        <v>9.833827318713155</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M45" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N45" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O45" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P45" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R45" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S45" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713164</v>
       </c>
     </row>
     <row r="46">
@@ -3150,34 +2602,22 @@
         <v>18.2232130384167</v>
       </c>
       <c r="J46" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K46" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L46" t="n">
-        <v>9.833827318713144</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M46" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N46" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O46" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P46" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R46" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S46" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713158</v>
       </c>
     </row>
     <row r="47">
@@ -3209,34 +2649,22 @@
         <v>18.21789083834707</v>
       </c>
       <c r="J47" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K47" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L47" t="n">
-        <v>9.833827318713151</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M47" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N47" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O47" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P47" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R47" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S47" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713144</v>
       </c>
     </row>
     <row r="48">
@@ -3268,34 +2696,22 @@
         <v>18.21257174613149</v>
       </c>
       <c r="J48" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K48" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L48" t="n">
-        <v>9.83382731871315</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M48" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N48" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O48" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P48" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R48" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S48" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713148</v>
       </c>
     </row>
     <row r="49">
@@ -3327,34 +2743,22 @@
         <v>18.20725575904856</v>
       </c>
       <c r="J49" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K49" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L49" t="n">
-        <v>9.833827318713164</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M49" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N49" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O49" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P49" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R49" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S49" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713158</v>
       </c>
     </row>
     <row r="50">
@@ -3386,34 +2790,22 @@
         <v>18.20194287438003</v>
       </c>
       <c r="J50" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K50" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L50" t="n">
-        <v>9.833827318713155</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M50" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N50" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O50" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P50" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R50" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S50" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.83382731871316</v>
       </c>
     </row>
     <row r="51">
@@ -3445,34 +2837,22 @@
         <v>18.19663308941085</v>
       </c>
       <c r="J51" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K51" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L51" t="n">
-        <v>9.833827318713137</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M51" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N51" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O51" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P51" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R51" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S51" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713148</v>
       </c>
     </row>
     <row r="52">
@@ -3504,34 +2884,22 @@
         <v>18.19132640142909</v>
       </c>
       <c r="J52" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K52" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L52" t="n">
-        <v>9.833827318713144</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M52" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N52" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O52" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P52" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R52" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S52" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713142</v>
       </c>
     </row>
     <row r="53">
@@ -3563,34 +2931,22 @@
         <v>18.18602280772606</v>
       </c>
       <c r="J53" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K53" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L53" t="n">
-        <v>9.833827318713151</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M53" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N53" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O53" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P53" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R53" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S53" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713137</v>
       </c>
     </row>
     <row r="54">
@@ -3622,34 +2978,22 @@
         <v>18.18072230559615</v>
       </c>
       <c r="J54" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K54" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L54" t="n">
-        <v>9.83382731871315</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M54" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N54" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O54" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P54" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R54" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S54" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713162</v>
       </c>
     </row>
     <row r="55">
@@ -3681,34 +3025,22 @@
         <v>18.17542489233694</v>
       </c>
       <c r="J55" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K55" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L55" t="n">
-        <v>9.833827318713141</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M55" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N55" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O55" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P55" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R55" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S55" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713158</v>
       </c>
     </row>
     <row r="56">
@@ -3740,34 +3072,22 @@
         <v>18.17013056524916</v>
       </c>
       <c r="J56" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K56" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L56" t="n">
-        <v>9.833827318713162</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M56" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N56" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O56" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P56" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R56" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S56" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713151</v>
       </c>
     </row>
     <row r="57">
@@ -3799,34 +3119,22 @@
         <v>18.16483932163668</v>
       </c>
       <c r="J57" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K57" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L57" t="n">
-        <v>9.833827318713144</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M57" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N57" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O57" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P57" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R57" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S57" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713146</v>
       </c>
     </row>
     <row r="58">
@@ -3858,34 +3166,22 @@
         <v>18.15955115880651</v>
       </c>
       <c r="J58" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K58" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L58" t="n">
-        <v>9.833827318713158</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M58" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N58" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O58" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P58" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R58" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S58" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713142</v>
       </c>
     </row>
     <row r="59">
@@ -3917,34 +3213,22 @@
         <v>18.15426607406879</v>
       </c>
       <c r="J59" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K59" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L59" t="n">
-        <v>9.83382731871315</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M59" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N59" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O59" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P59" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R59" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S59" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713153</v>
       </c>
     </row>
     <row r="60">
@@ -3976,34 +3260,22 @@
         <v>18.1489840647368</v>
       </c>
       <c r="J60" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K60" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L60" t="n">
-        <v>9.833827318713148</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M60" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N60" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O60" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P60" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R60" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S60" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713155</v>
       </c>
     </row>
     <row r="61">
@@ -4035,34 +3307,22 @@
         <v>18.14370512812693</v>
       </c>
       <c r="J61" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K61" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L61" t="n">
-        <v>9.833827318713155</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M61" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N61" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O61" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P61" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R61" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S61" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.83382731871315</v>
       </c>
     </row>
     <row r="62">
@@ -4094,34 +3354,22 @@
         <v>21.25939468798179</v>
       </c>
       <c r="J62" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K62" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L62" t="n">
-        <v>9.833827318713139</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M62" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N62" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O62" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P62" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R62" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S62" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713153</v>
       </c>
     </row>
     <row r="63">
@@ -4153,34 +3401,22 @@
         <v>21.25386989726247</v>
       </c>
       <c r="J63" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K63" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L63" t="n">
-        <v>9.833827318713144</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M63" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N63" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O63" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P63" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R63" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S63" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713155</v>
       </c>
     </row>
     <row r="64">
@@ -4212,34 +3448,22 @@
         <v>21.24834797730994</v>
       </c>
       <c r="J64" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K64" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L64" t="n">
-        <v>9.833827318713137</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M64" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N64" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O64" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P64" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R64" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S64" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713151</v>
       </c>
     </row>
     <row r="65">
@@ -4271,34 +3495,22 @@
         <v>21.24282892588726</v>
       </c>
       <c r="J65" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K65" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L65" t="n">
-        <v>9.833827318713157</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M65" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N65" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O65" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P65" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R65" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S65" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713166</v>
       </c>
     </row>
     <row r="66">
@@ -4330,34 +3542,22 @@
         <v>21.23731274075979</v>
       </c>
       <c r="J66" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K66" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L66" t="n">
+        <v>39.73509933774834</v>
+      </c>
+      <c r="M66" t="n">
+        <v>4.550991765900781</v>
+      </c>
+      <c r="N66" t="n">
+        <v>-36.14204360727691</v>
+      </c>
+      <c r="O66" t="n">
         <v>9.833827318713155</v>
-      </c>
-      <c r="M66" t="n">
-        <v>97.70163735096665</v>
-      </c>
-      <c r="N66" t="n">
-        <v>52.11057932438398</v>
-      </c>
-      <c r="O66" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P66" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R66" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S66" t="n">
-        <v>-36.14204360727691</v>
       </c>
     </row>
     <row r="67">
@@ -4389,34 +3589,22 @@
         <v>21.23179941969521</v>
       </c>
       <c r="J67" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K67" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L67" t="n">
-        <v>9.833827318713155</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M67" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N67" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O67" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P67" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R67" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S67" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.83382731871315</v>
       </c>
     </row>
     <row r="68">
@@ -4448,34 +3636,22 @@
         <v>21.22628896046353</v>
       </c>
       <c r="J68" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K68" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L68" t="n">
-        <v>9.833827318713153</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M68" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N68" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O68" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P68" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R68" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S68" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713158</v>
       </c>
     </row>
     <row r="69">
@@ -4507,34 +3683,22 @@
         <v>21.22078136083704</v>
       </c>
       <c r="J69" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K69" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L69" t="n">
-        <v>9.833827318713166</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M69" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N69" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O69" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P69" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R69" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S69" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713155</v>
       </c>
     </row>
     <row r="70">
@@ -4566,34 +3730,22 @@
         <v>21.21527661859039</v>
       </c>
       <c r="J70" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K70" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L70" t="n">
-        <v>9.833827318713157</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M70" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N70" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O70" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P70" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R70" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S70" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713164</v>
       </c>
     </row>
     <row r="71">
@@ -4625,34 +3777,22 @@
         <v>21.20977473150051</v>
       </c>
       <c r="J71" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K71" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L71" t="n">
-        <v>9.833827318713141</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M71" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N71" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O71" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P71" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R71" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S71" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.83382731871316</v>
       </c>
     </row>
     <row r="72">
@@ -4684,34 +3824,22 @@
         <v>21.20427569734663</v>
       </c>
       <c r="J72" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K72" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L72" t="n">
-        <v>9.833827318713148</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M72" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N72" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O72" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P72" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R72" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S72" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713132</v>
       </c>
     </row>
     <row r="73">
@@ -4743,34 +3871,22 @@
         <v>21.19877951391031</v>
       </c>
       <c r="J73" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K73" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L73" t="n">
-        <v>9.833827318713153</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M73" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N73" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O73" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P73" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R73" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S73" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713142</v>
       </c>
     </row>
     <row r="74">
@@ -4802,34 +3918,22 @@
         <v>21.19328617897537</v>
       </c>
       <c r="J74" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K74" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L74" t="n">
-        <v>9.833827318713146</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M74" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N74" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O74" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P74" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R74" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S74" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.83382731871316</v>
       </c>
     </row>
     <row r="75">
@@ -4861,34 +3965,22 @@
         <v>21.18779569032797</v>
       </c>
       <c r="J75" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K75" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L75" t="n">
-        <v>9.833827318713151</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M75" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N75" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O75" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P75" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R75" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S75" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.83382731871316</v>
       </c>
     </row>
     <row r="76">
@@ -4920,34 +4012,22 @@
         <v>21.18230804575653</v>
       </c>
       <c r="J76" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K76" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L76" t="n">
-        <v>9.833827318713148</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M76" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N76" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O76" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P76" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R76" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S76" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713142</v>
       </c>
     </row>
     <row r="77">
@@ -4979,34 +4059,22 @@
         <v>21.17682324305178</v>
       </c>
       <c r="J77" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K77" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L77" t="n">
-        <v>9.833827318713155</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M77" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N77" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O77" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P77" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R77" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S77" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713132</v>
       </c>
     </row>
     <row r="78">
@@ -5038,34 +4106,22 @@
         <v>21.17134128000672</v>
       </c>
       <c r="J78" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K78" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L78" t="n">
-        <v>9.833827318713146</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M78" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N78" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O78" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P78" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R78" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S78" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713141</v>
       </c>
     </row>
     <row r="79">
@@ -5097,34 +4153,22 @@
         <v>21.16586215441665</v>
       </c>
       <c r="J79" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K79" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L79" t="n">
-        <v>9.833827318713139</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M79" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N79" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O79" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P79" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R79" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S79" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713157</v>
       </c>
     </row>
     <row r="80">
@@ -5156,34 +4200,22 @@
         <v>21.16038586407917</v>
       </c>
       <c r="J80" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K80" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L80" t="n">
-        <v>9.833827318713151</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M80" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N80" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O80" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P80" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R80" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S80" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713144</v>
       </c>
     </row>
     <row r="81">
@@ -5215,34 +4247,22 @@
         <v>21.1549124067941</v>
       </c>
       <c r="J81" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K81" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L81" t="n">
-        <v>9.833827318713137</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M81" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N81" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O81" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P81" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R81" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S81" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713148</v>
       </c>
     </row>
     <row r="82">
@@ -5274,34 +4294,22 @@
         <v>21.14944178036358</v>
       </c>
       <c r="J82" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K82" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L82" t="n">
-        <v>9.833827318713155</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M82" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N82" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O82" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P82" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R82" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S82" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.83382731871315</v>
       </c>
     </row>
     <row r="83">
@@ -5333,34 +4341,22 @@
         <v>21.14397398259203</v>
       </c>
       <c r="J83" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K83" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L83" t="n">
-        <v>9.833827318713148</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M83" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N83" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O83" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P83" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R83" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S83" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713146</v>
       </c>
     </row>
     <row r="84">
@@ -5392,34 +4388,22 @@
         <v>21.13850901128611</v>
       </c>
       <c r="J84" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K84" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L84" t="n">
-        <v>9.833827318713153</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M84" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N84" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O84" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P84" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R84" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S84" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.83382731871316</v>
       </c>
     </row>
     <row r="85">
@@ -5451,34 +4435,22 @@
         <v>21.13304686425477</v>
       </c>
       <c r="J85" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K85" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L85" t="n">
-        <v>9.833827318713144</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M85" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N85" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O85" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P85" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R85" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S85" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713142</v>
       </c>
     </row>
     <row r="86">
@@ -5510,34 +4482,22 @@
         <v>21.12758753930921</v>
       </c>
       <c r="J86" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K86" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L86" t="n">
-        <v>9.833827318713158</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M86" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N86" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O86" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P86" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R86" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S86" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713144</v>
       </c>
     </row>
     <row r="87">
@@ -5569,34 +4529,22 @@
         <v>21.1221310342629</v>
       </c>
       <c r="J87" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K87" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L87" t="n">
-        <v>9.833827318713164</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M87" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N87" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O87" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P87" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R87" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S87" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713153</v>
       </c>
     </row>
     <row r="88">
@@ -5628,34 +4576,22 @@
         <v>21.11667734693156</v>
       </c>
       <c r="J88" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K88" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L88" t="n">
-        <v>9.833827318713142</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M88" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N88" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O88" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P88" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R88" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S88" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.83382731871315</v>
       </c>
     </row>
     <row r="89">
@@ -5687,34 +4623,22 @@
         <v>25.16901338497009</v>
       </c>
       <c r="J89" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K89" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L89" t="n">
-        <v>9.833827318713153</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M89" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N89" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O89" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P89" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R89" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S89" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713142</v>
       </c>
     </row>
     <row r="90">
@@ -5746,34 +4670,22 @@
         <v>25.16329835014153</v>
       </c>
       <c r="J90" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K90" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L90" t="n">
-        <v>9.833827318713166</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M90" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N90" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O90" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P90" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R90" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S90" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713151</v>
       </c>
     </row>
     <row r="91">
@@ -5805,34 +4717,22 @@
         <v>25.15758591010745</v>
       </c>
       <c r="J91" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K91" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L91" t="n">
-        <v>9.833827318713146</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M91" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N91" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O91" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P91" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R91" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S91" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713148</v>
       </c>
     </row>
     <row r="92">
@@ -5864,34 +4764,22 @@
         <v>25.15187606310107</v>
       </c>
       <c r="J92" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K92" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L92" t="n">
-        <v>9.833827318713158</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M92" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N92" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O92" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P92" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R92" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S92" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.83382731871315</v>
       </c>
     </row>
     <row r="93">
@@ -5923,34 +4811,22 @@
         <v>25.14616880735723</v>
       </c>
       <c r="J93" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K93" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L93" t="n">
-        <v>9.833827318713144</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M93" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N93" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O93" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P93" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R93" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S93" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713157</v>
       </c>
     </row>
     <row r="94">
@@ -5982,34 +4858,22 @@
         <v>25.14046414111236</v>
       </c>
       <c r="J94" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K94" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L94" t="n">
-        <v>9.833827318713153</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M94" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N94" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O94" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P94" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R94" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S94" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713139</v>
       </c>
     </row>
     <row r="95">
@@ -6041,34 +4905,22 @@
         <v>25.13476206260451</v>
       </c>
       <c r="J95" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K95" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L95" t="n">
-        <v>9.833827318713148</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M95" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N95" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O95" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P95" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R95" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S95" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.83382731871315</v>
       </c>
     </row>
     <row r="96">
@@ -6100,34 +4952,22 @@
         <v>25.12906257007331</v>
       </c>
       <c r="J96" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K96" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L96" t="n">
-        <v>9.833827318713146</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M96" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N96" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O96" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P96" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R96" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S96" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713144</v>
       </c>
     </row>
     <row r="97">
@@ -6159,34 +4999,22 @@
         <v>25.12336566175998</v>
       </c>
       <c r="J97" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K97" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L97" t="n">
-        <v>9.833827318713158</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M97" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N97" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O97" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P97" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R97" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S97" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713141</v>
       </c>
     </row>
     <row r="98">
@@ -6218,34 +5046,22 @@
         <v>25.11767133590737</v>
       </c>
       <c r="J98" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K98" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L98" t="n">
-        <v>9.833827318713162</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M98" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N98" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O98" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P98" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R98" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S98" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.83382731871316</v>
       </c>
     </row>
     <row r="99">
@@ -6277,34 +5093,22 @@
         <v>25.11197959075987</v>
       </c>
       <c r="J99" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K99" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L99" t="n">
-        <v>9.83382731871315</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M99" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N99" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O99" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P99" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R99" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S99" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713144</v>
       </c>
     </row>
     <row r="100">
@@ -6336,34 +5140,22 @@
         <v>25.1062904245635</v>
       </c>
       <c r="J100" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K100" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L100" t="n">
-        <v>9.833827318713148</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M100" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N100" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O100" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P100" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R100" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S100" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713146</v>
       </c>
     </row>
     <row r="101">
@@ -6395,34 +5187,22 @@
         <v>25.10060383556587</v>
       </c>
       <c r="J101" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K101" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L101" t="n">
-        <v>9.833827318713148</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M101" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N101" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O101" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P101" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R101" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S101" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713142</v>
       </c>
     </row>
     <row r="102">
@@ -6454,34 +5234,22 @@
         <v>25.09491982201615</v>
       </c>
       <c r="J102" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K102" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L102" t="n">
+        <v>39.73509933774834</v>
+      </c>
+      <c r="M102" t="n">
+        <v>4.550991765900781</v>
+      </c>
+      <c r="N102" t="n">
+        <v>-36.14204360727691</v>
+      </c>
+      <c r="O102" t="n">
         <v>9.833827318713151</v>
-      </c>
-      <c r="M102" t="n">
-        <v>97.70163735096665</v>
-      </c>
-      <c r="N102" t="n">
-        <v>52.11057932438398</v>
-      </c>
-      <c r="O102" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P102" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R102" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S102" t="n">
-        <v>-36.14204360727691</v>
       </c>
     </row>
     <row r="103">
@@ -6513,34 +5281,22 @@
         <v>25.08923838216511</v>
       </c>
       <c r="J103" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K103" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L103" t="n">
-        <v>9.833827318713137</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M103" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N103" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O103" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P103" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R103" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S103" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713158</v>
       </c>
     </row>
     <row r="104">
@@ -6572,34 +5328,22 @@
         <v>25.08355951426512</v>
       </c>
       <c r="J104" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K104" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L104" t="n">
-        <v>9.833827318713162</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M104" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N104" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O104" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P104" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R104" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S104" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713148</v>
       </c>
     </row>
     <row r="105">
@@ -6631,34 +5375,22 @@
         <v>25.0778832165701</v>
       </c>
       <c r="J105" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K105" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L105" t="n">
-        <v>9.833827318713155</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M105" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N105" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O105" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P105" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R105" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S105" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713144</v>
       </c>
     </row>
     <row r="106">
@@ -6690,34 +5422,22 @@
         <v>25.07220948733559</v>
       </c>
       <c r="J106" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K106" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L106" t="n">
-        <v>9.833827318713153</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M106" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N106" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O106" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P106" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R106" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S106" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713141</v>
       </c>
     </row>
     <row r="107">
@@ -6749,34 +5469,22 @@
         <v>25.06653832481866</v>
       </c>
       <c r="J107" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K107" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L107" t="n">
-        <v>9.833827318713158</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M107" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N107" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O107" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P107" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R107" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S107" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713155</v>
       </c>
     </row>
     <row r="108">
@@ -6808,34 +5516,22 @@
         <v>25.060869727278</v>
       </c>
       <c r="J108" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K108" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L108" t="n">
-        <v>9.833827318713151</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M108" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N108" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O108" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P108" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R108" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S108" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713162</v>
       </c>
     </row>
     <row r="109">
@@ -6867,34 +5563,22 @@
         <v>25.05520369297384</v>
       </c>
       <c r="J109" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K109" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L109" t="n">
-        <v>9.83382731871315</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M109" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N109" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O109" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P109" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R109" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S109" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713146</v>
       </c>
     </row>
     <row r="110">
@@ -6926,34 +5610,22 @@
         <v>25.04954022016802</v>
       </c>
       <c r="J110" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K110" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L110" t="n">
-        <v>9.833827318713137</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M110" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N110" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O110" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P110" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R110" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S110" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713142</v>
       </c>
     </row>
     <row r="111">
@@ -6985,34 +5657,22 @@
         <v>25.04387930712391</v>
       </c>
       <c r="J111" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K111" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L111" t="n">
-        <v>9.833827318713155</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M111" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N111" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O111" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P111" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R111" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S111" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713137</v>
       </c>
     </row>
     <row r="112">
@@ -7044,34 +5704,22 @@
         <v>25.03822095210648</v>
       </c>
       <c r="J112" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K112" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L112" t="n">
-        <v>9.833827318713146</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M112" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N112" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O112" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P112" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R112" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S112" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713151</v>
       </c>
     </row>
     <row r="113">
@@ -7103,34 +5751,22 @@
         <v>25.03256515338227</v>
       </c>
       <c r="J113" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K113" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L113" t="n">
-        <v>9.833827318713151</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M113" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N113" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O113" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P113" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R113" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S113" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713153</v>
       </c>
     </row>
     <row r="114">
@@ -7162,34 +5798,22 @@
         <v>25.02691190921935</v>
       </c>
       <c r="J114" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K114" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L114" t="n">
-        <v>9.83382731871315</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M114" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N114" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O114" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P114" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R114" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S114" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713144</v>
       </c>
     </row>
     <row r="115">
@@ -7221,34 +5845,22 @@
         <v>25.0212612178874</v>
       </c>
       <c r="J115" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K115" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L115" t="n">
-        <v>9.833827318713157</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M115" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N115" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O115" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P115" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R115" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S115" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713158</v>
       </c>
     </row>
     <row r="116">
@@ -7280,34 +5892,22 @@
         <v>25.01561307765763</v>
       </c>
       <c r="J116" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K116" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L116" t="n">
-        <v>9.833827318713142</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M116" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N116" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O116" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P116" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R116" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S116" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713146</v>
       </c>
     </row>
     <row r="117">
@@ -7339,34 +5939,22 @@
         <v>25.00996748680283</v>
       </c>
       <c r="J117" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K117" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L117" t="n">
-        <v>9.833827318713142</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M117" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N117" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O117" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P117" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R117" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S117" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713157</v>
       </c>
     </row>
     <row r="118">
@@ -7398,34 +5986,22 @@
         <v>25.00432444359732</v>
       </c>
       <c r="J118" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K118" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L118" t="n">
-        <v>9.833827318713146</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M118" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N118" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O118" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P118" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R118" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S118" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713144</v>
       </c>
     </row>
     <row r="119">
@@ -7457,34 +6033,22 @@
         <v>24.99868394631701</v>
       </c>
       <c r="J119" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K119" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L119" t="n">
-        <v>9.833827318713158</v>
+        <v>39.73509933774834</v>
       </c>
       <c r="M119" t="n">
-        <v>97.70163735096665</v>
+        <v>4.550991765900781</v>
       </c>
       <c r="N119" t="n">
-        <v>52.11057932438398</v>
+        <v>-36.14204360727691</v>
       </c>
       <c r="O119" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P119" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R119" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S119" t="n">
-        <v>-36.14204360727691</v>
+        <v>9.833827318713142</v>
       </c>
     </row>
     <row r="120">
@@ -7516,34 +6080,22 @@
         <v>24.99304599323936</v>
       </c>
       <c r="J120" t="n">
-        <v>153.1265226962625</v>
+        <v>119.205298013245</v>
       </c>
       <c r="K120" t="n">
-        <v>119.205298013245</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="L120" t="n">
+        <v>39.73509933774834</v>
+      </c>
+      <c r="M120" t="n">
+        <v>4.550991765900781</v>
+      </c>
+      <c r="N120" t="n">
+        <v>-36.14204360727691</v>
+      </c>
+      <c r="O120" t="n">
         <v>9.83382731871315</v>
-      </c>
-      <c r="M120" t="n">
-        <v>97.70163735096665</v>
-      </c>
-      <c r="N120" t="n">
-        <v>52.11057932438398</v>
-      </c>
-      <c r="O120" t="n">
-        <v>143.2926953775493</v>
-      </c>
-      <c r="P120" t="n">
-        <v>45.59105802658267</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>39.73509933774834</v>
-      </c>
-      <c r="R120" t="n">
-        <v>4.550991765900781</v>
-      </c>
-      <c r="S120" t="n">
-        <v>-36.14204360727691</v>
       </c>
     </row>
   </sheetData>
